--- a/assets/templates/MultiDeviceReturnsTemplate.xlsx
+++ b/assets/templates/MultiDeviceReturnsTemplate.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://radiuspaymentsolutions750-my.sharepoint.com/personal/souhaib_mahli_radius_com/Documents/Bureaublad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amira/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{014ED4F4-A9C7-4C46-BEEB-ECA1016A3102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB69DB5A-D98C-FB4E-BB93-86B22EFE22D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44880" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{A794375F-B85A-4CEF-B2F5-D130DB419625}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18880" xr2:uid="{A794375F-B85A-4CEF-B2F5-D130DB419625}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Return_Reasons" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>RETURNED</t>
   </si>
@@ -75,6 +76,54 @@
   </si>
   <si>
     <t>GRADE_W</t>
+  </si>
+  <si>
+    <t>Returned device</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Fleet reductions/too many devices</t>
+  </si>
+  <si>
+    <t>Replacement (wrong device/swap out)</t>
+  </si>
+  <si>
+    <t>Service/Installation issues</t>
+  </si>
+  <si>
+    <t>Moving to competitor/price</t>
+  </si>
+  <si>
+    <t>Don't see value</t>
+  </si>
+  <si>
+    <t>Need more functionality</t>
+  </si>
+  <si>
+    <t>Account Transfer</t>
+  </si>
+  <si>
+    <t>Device Transfer</t>
+  </si>
+  <si>
+    <t>Business Closure</t>
+  </si>
+  <si>
+    <t>Returned to Sender</t>
+  </si>
+  <si>
+    <t>Credit Stop – Fraud</t>
+  </si>
+  <si>
+    <t>Credit Stop - Insolvency/administration</t>
+  </si>
+  <si>
+    <t>Credit Stop – Non payer/exhausted all recoveries</t>
+  </si>
+  <si>
+    <t>RETURN REASON</t>
   </si>
 </sst>
 </file>
@@ -118,215 +167,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -431,7 +286,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -727,330 +582,495 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A5BAB9-8A0A-4A39-A770-EA135174BC28}">
-  <dimension ref="A1:L55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M82"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="3" customWidth="1"/>
-    <col min="2" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" style="3" customWidth="1"/>
-    <col min="7" max="8" width="22.88671875" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" customWidth="1"/>
-    <col min="11" max="11" width="16.77734375" customWidth="1"/>
-    <col min="12" max="12" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" customWidth="1"/>
+    <col min="8" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="C5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="C11" s="4"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="C12" s="4"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="C13" s="4"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="C14" s="4"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="C15" s="4"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="C16" s="4"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="C17" s="4"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="C18" s="4"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="C19" s="4"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="C20" s="4"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="C31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="C34" s="4"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="C35" s="4"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="C36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="C37" s="4"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="C38" s="4"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="C39" s="4"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="C40" s="4"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="C41" s="4"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="C42" s="4"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="4"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C48" s="4"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" s="4"/>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" s="4"/>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="4"/>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C55" s="4"/>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D2" s="3"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D3" s="3"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D4" s="3"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D5" s="3"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D6" s="4"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D7" s="4"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D8" s="4"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D9" s="4"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D10" s="4"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D11" s="4"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D12" s="4"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D13" s="4"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D14" s="4"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D15" s="4"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D16" s="4"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D17" s="4"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D18" s="4"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D22" s="4"/>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D24" s="4"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D29" s="3"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D30" s="3"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D82" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A20">
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A43">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C10">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C55">
-    <cfRule type="duplicateValues" dxfId="11" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="G26:G27">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F16">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  <conditionalFormatting sqref="G30:G40">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F20">
-    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  <conditionalFormatting sqref="G41:G44">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44B83E31-74D4-46A5-8039-96C1E6A90051}">
+          <x14:formula1>
+            <xm:f>Return_Reasons!$A$1:$A$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9A575D-5F56-4D1C-8040-3C24DE104D68}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="51.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>10003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>10005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>10006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>10007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>10008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>10009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>10013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>10014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
+        <v>10015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>